--- a/Result/profitability/9905.xlsx
+++ b/Result/profitability/9905.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.19</v>
       </c>
       <c r="M2" t="n">
-        <v>0.34375</v>
+        <v>0.33375</v>
       </c>
       <c r="N2" t="n">
-        <v>10.5075</v>
+        <v>10.38625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.47</v>
       </c>
       <c r="M3" t="n">
-        <v>0.32625</v>
+        <v>0.35375</v>
       </c>
       <c r="N3" t="n">
-        <v>10.90125</v>
+        <v>11.095</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -801,7 +801,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.61</v>
       </c>
       <c r="M4" t="n">
-        <v>0.36375</v>
+        <v>0.4</v>
       </c>
       <c r="N4" t="n">
-        <v>12.13375</v>
+        <v>12.59875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.34</v>
       </c>
       <c r="M5" t="n">
-        <v>0.29125</v>
+        <v>0.32</v>
       </c>
       <c r="N5" t="n">
-        <v>11.73875</v>
+        <v>12.03125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0.285</v>
+        <v>0.2975</v>
       </c>
       <c r="N6" t="n">
-        <v>12.29375</v>
+        <v>12.6325</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.64</v>
       </c>
       <c r="M7" t="n">
-        <v>0.31125</v>
+        <v>0.3375</v>
       </c>
       <c r="N7" t="n">
-        <v>13.61625</v>
+        <v>13.8975</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.59</v>
       </c>
       <c r="M8" t="n">
-        <v>0.345</v>
+        <v>0.3675</v>
       </c>
       <c r="N8" t="n">
-        <v>14.94</v>
+        <v>15.22875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9905</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2797</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2451</v>
+      </c>
+      <c r="E75" t="n">
+        <v>346</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="G75" t="n">
+        <v>208</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.45%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>18</v>
+      </c>
+      <c r="J75" t="n">
+        <v>227</v>
+      </c>
+      <c r="K75" t="n">
+        <v>163</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.64125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5142857142857145</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2293942403177756</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.7666666666666668</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.340000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2330677290836656</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
